--- a/SPAS-META相关_Final.xlsx
+++ b/SPAS-META相关_Final.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25320" windowHeight="12140" activeTab="1"/>
+    <workbookView windowWidth="25340" windowHeight="12160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="zoey" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="51">
   <si>
     <t>PICOS+关键词</t>
   </si>
@@ -213,6 +213,9 @@
     <t>PICOS原则：红色部分是我建议纳入检索框的模块</t>
   </si>
   <si>
+    <t>优化</t>
+  </si>
+  <si>
     <t>备注</t>
   </si>
   <si>
@@ -228,10 +231,20 @@
 OR "Women's Group"[Title/Abstract]</t>
   </si>
   <si>
+    <t>"Female" OR "Girl" OR "Woman" OR "Women's Group"</t>
+  </si>
+  <si>
     <t>检索阶段是否可以把P（female）模块从AND逻辑里去掉，从而避免漏掉那些题目摘要里没提性别但是正文里有可提取女性数据的研究。针对混合样本，若正文附录报告了按性别拆分的数据，便纳入且只提取女性亚组的效应量数据；若未报告性别拆分数据，但女性占比可辨识，便联系作者索要未发表的性别拆分数据</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>考虑检索的文献库：</t>
     </r>
     <r>
@@ -313,7 +326,15 @@
 OR "Training, Human Physical"[Title/Abstract]
 5. "Motor Activity"[Mesh]: "Activities, Motor"[Title/Abstract]
 OR "Activity, Motor"[Title/Abstract]
-OR "Motor Activities"[Title/Abstract]</t>
+OR "Motor Activities"[Title/Abstract]
+6. Others: OR "yoga"[Title/Abstract]
+OR "pilates"[Title/Abstract]
+OR "dance"[Title/Abstract]
+OR "dancing"[Title/Abstract]
+OR "fitness"[Title/Abstract]</t>
+  </si>
+  <si>
+    <t>“Sport" OR "Athletic" OR "Exercise" OR "Physical Exercise" OR "Isometric Exercise" OR "Aerobic Exercise" OR "Exercise Training" OR "Physical Activity" OR "Active Break" OR "Acute Exercise" OR "Exercise Therapy" OR "Exercise Prescription" OR "Rehabilitation Exercise" OR "Remedial Exercise" OR "Exercise Therapy" OR "Physical Activity Intervention" OR "Human Physical Conditioning" OR "Human Physical Training" OR "Motor Activity" OR "yoga" OR "pilates" OR "dance" OR "dancing" OR "fitness" OR "dance movement" OR "dance movement therapy"</t>
   </si>
   <si>
     <t>"social physique anxiety"[Title/Abstract]
@@ -324,10 +345,22 @@
 OR "SPAS-7"[Title/Abstract]</t>
   </si>
   <si>
+    <t>"social physique anxiety" OR "social physical anxiety" OR "physique anxiety" OR "Social Physique Anxiety Scale" OR "SPAS" OR "SPAS-7" OR "anxiety" OR "social anxiety" OR "physical activity and anxiety" OR "anxiety about body" OR "body image" OR "self-consciousness" OR "anxiousness"</t>
+  </si>
+  <si>
     <t>Mesh医学词库没有相关的词汇</t>
   </si>
   <si>
     <r>
+      <rPr>
+        <b/>
+        <u/>
+        <sz val="18"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>中文纳入标准</t>
     </r>
     <r>
@@ -627,6 +660,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="18"/>
       <color theme="1"/>
@@ -634,20 +674,25 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1005,7 +1050,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1029,16 +1074,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1047,90 +1092,93 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1142,26 +1190,44 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1703,124 +1769,124 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="26" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="41.0192307692308" style="10" customWidth="1"/>
-    <col min="2" max="2" width="196.442307692308" style="10" customWidth="1"/>
-    <col min="3" max="3" width="254.875" style="10" customWidth="1"/>
-    <col min="4" max="16384" width="9.23076923076923" style="10"/>
+    <col min="1" max="1" width="41.0192307692308" style="15" customWidth="1"/>
+    <col min="2" max="2" width="196.442307692308" style="15" customWidth="1"/>
+    <col min="3" max="3" width="254.875" style="15" customWidth="1"/>
+    <col min="4" max="16384" width="9.23076923076923" style="15"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="19" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" ht="182" spans="1:3">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="13"/>
+      <c r="C2" s="20"/>
     </row>
     <row r="3" ht="409" customHeight="1" spans="1:3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13"/>
+      <c r="C3" s="20"/>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="13"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="20"/>
     </row>
     <row r="5" ht="78" spans="1:3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="13"/>
+      <c r="C5" s="20"/>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="14"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="21"/>
     </row>
     <row r="11" ht="409" customHeight="1" spans="1:3">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C11" s="14" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="104" spans="1:3">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="9" t="s">
+      <c r="C14" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" ht="104" spans="1:3">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="14" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" ht="78" spans="1:3">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="9" t="s">
+      <c r="B16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="9" t="s">
+      <c r="C16" s="14" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="18" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" ht="338" spans="1:3">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="9" t="s">
+      <c r="B20" s="14" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="9" t="s">
+      <c r="C20" s="14" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1836,158 +1902,183 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E18"/>
-  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="4"/>
+  <dimension ref="A1:F18"/>
+  <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="16.8" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="37.0192307692308" customWidth="1"/>
     <col min="2" max="2" width="91.3461538461538" customWidth="1"/>
-    <col min="3" max="3" width="73.9807692307692" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.2692307692308" style="1" customWidth="1"/>
-    <col min="5" max="5" width="28.2019230769231" customWidth="1"/>
+    <col min="3" max="3" width="91.3461538461538" style="1" customWidth="1"/>
+    <col min="4" max="4" width="73.9807692307692" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.2692307692308" style="2" customWidth="1"/>
+    <col min="6" max="6" width="28.2019230769231" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="57" customHeight="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+    <row r="1" ht="57" customHeight="1" spans="1:6">
+      <c r="A1" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="2" ht="202" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="E1" s="2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="2" ht="182" spans="1:6">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="B2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="6" t="s">
+      <c r="C2" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="3" ht="409.5" spans="1:5">
-      <c r="A3" s="2" t="s">
+      <c r="D2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="409.5" spans="1:6">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" ht="26" spans="1:5">
-      <c r="A4" s="4" t="s">
+      <c r="B3" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="7"/>
+    </row>
+    <row r="4" ht="26" spans="1:6">
+      <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="3"/>
-    </row>
-    <row r="5" ht="156" spans="1:5">
-      <c r="A5" s="2" t="s">
+      <c r="B4" s="4"/>
+      <c r="C4" s="5"/>
+    </row>
+    <row r="5" ht="156" spans="1:6">
+      <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" ht="26" spans="1:5">
-      <c r="A6" s="4" t="s">
+      <c r="B5" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" ht="26" spans="1:6">
+      <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3"/>
-    </row>
-    <row r="9" ht="409" customHeight="1" spans="1:5">
-      <c r="A9" s="7" t="s">
+      <c r="B6" s="4"/>
+      <c r="C6" s="5"/>
+    </row>
+    <row r="9" ht="409" customHeight="1" spans="1:6">
+      <c r="A9" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" ht="26" spans="1:5">
-      <c r="A10" s="10"/>
-      <c r="B10" s="10"/>
-      <c r="C10" s="10"/>
-    </row>
-    <row r="11" ht="26" spans="1:5">
-      <c r="A11" s="10"/>
-      <c r="B11" s="10"/>
-      <c r="C11" s="10"/>
-    </row>
-    <row r="12" ht="260" spans="1:5">
-      <c r="A12" s="7" t="s">
+      <c r="B9" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" s="13"/>
+      <c r="D9" s="14" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="10" ht="26" spans="1:6">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="16"/>
+      <c r="D10" s="15"/>
+    </row>
+    <row r="11" ht="26" spans="1:6">
+      <c r="A11" s="15"/>
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="15"/>
+    </row>
+    <row r="12" ht="260" spans="1:6">
+      <c r="A12" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" ht="260" spans="1:5">
-      <c r="A13" s="7" t="s">
+      <c r="B12" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="17"/>
+      <c r="D12" s="14" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="13" ht="260" spans="1:6">
+      <c r="A13" s="11" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" ht="182" spans="1:5">
-      <c r="A14" s="7" t="s">
+      <c r="B13" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="17"/>
+      <c r="D13" s="14" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" ht="182" spans="1:6">
+      <c r="A14" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="15" ht="26" spans="1:5">
-      <c r="A15" s="10"/>
-      <c r="B15" s="10"/>
-      <c r="C15" s="10"/>
-    </row>
-    <row r="16" ht="26" spans="1:5">
-      <c r="A16" s="7" t="s">
+      <c r="B14" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="C14" s="17"/>
+      <c r="D14" s="14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="15" ht="26" spans="1:6">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="15"/>
+    </row>
+    <row r="16" ht="26" spans="1:6">
+      <c r="A16" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="10"/>
-    </row>
-    <row r="17" ht="26" spans="1:3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-    </row>
-    <row r="18" ht="409.5" spans="1:3">
-      <c r="A18" s="11" t="s">
+      <c r="C16" s="16"/>
+      <c r="D16" s="15"/>
+    </row>
+    <row r="17" ht="26" spans="1:4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="15"/>
+    </row>
+    <row r="18" ht="409.5" spans="1:4">
+      <c r="A18" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>46</v>
+      <c r="B18" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="14" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/SPAS-META相关_Final.xlsx
+++ b/SPAS-META相关_Final.xlsx
@@ -345,7 +345,7 @@
 OR "SPAS-7"[Title/Abstract]</t>
   </si>
   <si>
-    <t>"social physique anxiety" OR "social physical anxiety" OR "physique anxiety" OR "Social Physique Anxiety Scale" OR "SPAS" OR "SPAS-7" OR "anxiety" OR "social anxiety" OR "physical activity and anxiety" OR "anxiety about body" OR "body image" OR "self-consciousness" OR "anxiousness"</t>
+    <t>"social physique anxiety" OR "social physical anxiety" OR "physique anxiety" OR "Social Physique Anxiety Scale" OR "SPAS" OR "SPAS-7" OR "anxiety" OR "social anxiety" OR "physical activity and anxiety" OR "anxiety about body" OR "body image"</t>
   </si>
   <si>
     <t>Mesh医学词库没有相关的词汇</t>
@@ -660,13 +660,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="18"/>
       <color theme="1"/>
@@ -674,19 +667,20 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1050,7 +1044,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1074,16 +1068,16 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="9" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1092,89 +1086,89 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1204,9 +1198,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
@@ -1769,10 +1760,10 @@
   <dimension ref="A1:C20"/>
   <sheetFormatPr defaultColWidth="9.23076923076923" defaultRowHeight="26" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="41.0192307692308" style="15" customWidth="1"/>
-    <col min="2" max="2" width="196.442307692308" style="15" customWidth="1"/>
-    <col min="3" max="3" width="254.875" style="15" customWidth="1"/>
-    <col min="4" max="16384" width="9.23076923076923" style="15"/>
+    <col min="1" max="1" width="41.0192307692308" style="14" customWidth="1"/>
+    <col min="2" max="2" width="196.442307692308" style="14" customWidth="1"/>
+    <col min="3" max="3" width="254.875" style="14" customWidth="1"/>
+    <col min="4" max="16384" width="9.23076923076923" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1782,7 +1773,7 @@
       <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="18" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1793,7 +1784,7 @@
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="20"/>
+      <c r="C2" s="19"/>
     </row>
     <row r="3" ht="409" customHeight="1" spans="1:3">
       <c r="A3" s="6" t="s">
@@ -1802,14 +1793,14 @@
       <c r="B3" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="20"/>
+      <c r="C3" s="19"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="6" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="4"/>
-      <c r="C4" s="20"/>
+      <c r="C4" s="19"/>
     </row>
     <row r="5" ht="78" spans="1:3">
       <c r="A5" s="6" t="s">
@@ -1818,75 +1809,75 @@
       <c r="B5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="20"/>
+      <c r="C5" s="19"/>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="21"/>
+      <c r="C6" s="20"/>
     </row>
     <row r="11" ht="409" customHeight="1" spans="1:3">
-      <c r="A11" s="11" t="s">
+      <c r="A11" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="14" ht="104" spans="1:3">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="13" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="15" ht="104" spans="1:3">
-      <c r="A15" s="11" t="s">
+      <c r="A15" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="14" t="s">
+      <c r="B15" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="C15" s="14" t="s">
+      <c r="C15" s="13" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="16" ht="78" spans="1:3">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:3">
-      <c r="A18" s="11" t="s">
+      <c r="A18" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="17" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="20" ht="338" spans="1:3">
-      <c r="A20" s="18" t="s">
+      <c r="A20" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B20" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="13" t="s">
         <v>27</v>
       </c>
     </row>
@@ -1954,7 +1945,7 @@
       <c r="B3" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="8" t="s">
         <v>37</v>
       </c>
       <c r="D3" s="7"/>
@@ -1988,96 +1979,96 @@
       <c r="C6" s="5"/>
     </row>
     <row r="9" ht="409" customHeight="1" spans="1:6">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="14" t="s">
+      <c r="C9" s="12"/>
+      <c r="D9" s="13" t="s">
         <v>42</v>
       </c>
     </row>
     <row r="10" ht="26" spans="1:6">
-      <c r="A10" s="15"/>
-      <c r="B10" s="15"/>
-      <c r="C10" s="16"/>
-      <c r="D10" s="15"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="15"/>
+      <c r="D10" s="14"/>
     </row>
     <row r="11" ht="26" spans="1:6">
-      <c r="A11" s="15"/>
-      <c r="B11" s="15"/>
-      <c r="C11" s="16"/>
-      <c r="D11" s="15"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="15"/>
+      <c r="D11" s="14"/>
     </row>
     <row r="12" ht="260" spans="1:6">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="B12" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="14" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="13" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" ht="260" spans="1:6">
-      <c r="A13" s="11" t="s">
+      <c r="A13" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B13" s="14" t="s">
+      <c r="B13" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="14" t="s">
+      <c r="C13" s="16"/>
+      <c r="D13" s="13" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" ht="182" spans="1:6">
-      <c r="A14" s="11" t="s">
+      <c r="A14" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B14" s="14" t="s">
+      <c r="B14" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="14" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="13" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="15" ht="26" spans="1:6">
-      <c r="A15" s="15"/>
-      <c r="B15" s="15"/>
-      <c r="C15" s="16"/>
-      <c r="D15" s="15"/>
+      <c r="A15" s="14"/>
+      <c r="B15" s="14"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="14"/>
     </row>
     <row r="16" ht="26" spans="1:6">
-      <c r="A16" s="11" t="s">
+      <c r="A16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="C16" s="16"/>
-      <c r="D16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="14"/>
     </row>
     <row r="17" ht="26" spans="1:4">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="15"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="14"/>
     </row>
     <row r="18" ht="409.5" spans="1:4">
-      <c r="A18" s="18" t="s">
+      <c r="A18" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="14" t="s">
+      <c r="C18" s="16"/>
+      <c r="D18" s="13" t="s">
         <v>50</v>
       </c>
     </row>
